--- a/data/S2015_16_FINAL.xlsx
+++ b/data/S2015_16_FINAL.xlsx
@@ -1,35 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_liga" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_1liga" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_2liga" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KVAL" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30PRAH" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30STRC" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30JHCK" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30PLZN" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30KVRY" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30USTE" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30LIBE" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30HRAD" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30PARD" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30VYSO" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30JHMR" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30SVMR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTES" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SYSTEM" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SERIES" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CLUBS" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="META" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="10_liga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="20_1liga" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="30_2liga" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="KVAL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="30PRAH" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="30STRC" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="30JHCK" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="30PLZN" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="30KVRY" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="30USTE" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="30LIBE" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="30HRAD" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="30PARD" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="30VYSO" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="30JHMR" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="30SVMR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="NOTES" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="SYSTEM" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="SERIES" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="CLUBS" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="META" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -37,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +55,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +77,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -83,11 +95,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -13217,7 +13235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13261,6 +13279,23 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0031</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K222"/>
+  <dimension ref="A1:L222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13334,6 +13369,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13371,6 +13411,11 @@
           <t>14 týmů (4-col): základ + předkolo/QF/SF/finále + Play Out + baráž. Mistr: Bílí Tygři Liberec.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13408,6 +13453,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13445,6 +13495,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13482,6 +13537,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13519,6 +13579,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13556,6 +13621,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13593,6 +13663,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13630,6 +13705,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13667,6 +13747,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13704,6 +13789,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13741,6 +13831,11 @@
           <t>1.liga: základ + QF/SF + Play out + baráž.</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13778,6 +13873,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13815,6 +13915,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13852,6 +13957,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13889,6 +13999,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13926,6 +14041,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13963,6 +14083,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14000,6 +14125,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14037,6 +14167,11 @@
           <t>II.liga: skupiny + QF/SF/finále + baráž o 2.ligu.</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14074,6 +14209,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14111,6 +14251,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14148,6 +14293,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -14185,6 +14335,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -14222,6 +14377,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -14259,6 +14419,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -14296,6 +14461,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -14333,6 +14503,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -14370,6 +14545,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -14407,6 +14587,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -14444,6 +14629,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -14476,6 +14666,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0031</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -14513,6 +14708,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0032</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -14550,6 +14750,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0033</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -14587,6 +14792,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0034</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -14624,6 +14834,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0036</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -14698,6 +14913,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0038</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -14767,6 +14987,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0040</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -14804,6 +15029,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0041</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -14989,6 +15219,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0152</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -15206,6 +15441,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0045</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -15719,6 +15959,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0059</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -16195,6 +16440,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0072</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -17522,6 +17772,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0130</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -18326,6 +18581,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0134</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -18548,6 +18808,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0152</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -18802,6 +19067,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0143</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -19283,6 +19553,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0158</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -19394,6 +19669,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0161</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -19426,6 +19706,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0162</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -19574,6 +19859,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0166</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -20055,6 +20345,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0179</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -20531,6 +20826,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0196</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -20933,6 +21233,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0208</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -21407,6 +21712,11 @@
       <c r="J221" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0223</t>
         </is>
       </c>
     </row>
@@ -39585,6 +39895,81 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0031</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2015_16_FINAL.xlsx
+++ b/data/S2015_16_FINAL.xlsx
@@ -13310,7 +13310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L222"/>
+  <dimension ref="A1:N222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13372,6 +13372,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S2015_16_FINAL.xlsx
+++ b/data/S2015_16_FINAL.xlsx
@@ -13458,6 +13458,16 @@
           <t>NODE_S2015_16_0001</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0004</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0009</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13467,6 +13477,14 @@
         <is>
           <t>NODE_S2014_15_0002</t>
         </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -13542,6 +13560,16 @@
           <t>NODE_S2015_16_0003</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0005</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0009</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13551,6 +13579,14 @@
         <is>
           <t>NODE_S2014_15_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -13584,6 +13620,12 @@
           <t>NODE_S2015_16_0003</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0006</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13593,6 +13635,14 @@
         <is>
           <t>NODE_S2014_15_0005</t>
         </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -13626,6 +13676,16 @@
           <t>NODE_S2015_16_0003</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0008</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0007</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13635,6 +13695,14 @@
         <is>
           <t>NODE_S2014_15_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -13668,6 +13736,8 @@
           <t>NODE_S2015_16_0003</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13677,6 +13747,14 @@
         <is>
           <t>NODE_S2014_15_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -13710,6 +13788,8 @@
           <t>NODE_S2015_16_0003</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13719,6 +13799,14 @@
         <is>
           <t>NODE_S2014_15_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -13752,6 +13840,8 @@
           <t>NODE_S2015_16_0001</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13761,6 +13851,14 @@
         <is>
           <t>NODE_S2014_15_0009</t>
         </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -13878,6 +13976,16 @@
           <t>NODE_S2015_16_0011</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0013</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0017</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13887,6 +13995,14 @@
         <is>
           <t>NODE_S2014_15_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -13920,6 +14036,16 @@
           <t>NODE_S2015_16_0011</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0014</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0017</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13929,6 +14055,14 @@
         <is>
           <t>NODE_S2014_15_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -13962,6 +14096,12 @@
           <t>NODE_S2015_16_0011</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0015</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13971,6 +14111,14 @@
         <is>
           <t>NODE_S2014_15_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -14004,6 +14152,12 @@
           <t>NODE_S2015_16_0011</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0016</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14013,6 +14167,14 @@
         <is>
           <t>NODE_S2014_15_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -14046,6 +14208,8 @@
           <t>NODE_S2015_16_0011</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14055,6 +14219,14 @@
         <is>
           <t>NODE_S2014_15_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -14088,6 +14260,8 @@
           <t>NODE_S2015_16_0011</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14097,6 +14271,14 @@
         <is>
           <t>NODE_S2014_15_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -14382,6 +14564,12 @@
           <t>NODE_S2015_16_0019</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14391,6 +14579,14 @@
         <is>
           <t>NODE_S2014_15_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -14424,6 +14620,12 @@
           <t>NODE_S2015_16_0019</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14433,6 +14635,14 @@
         <is>
           <t>NODE_S2014_15_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -14466,6 +14676,12 @@
           <t>NODE_S2015_16_0019</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0027</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14475,6 +14691,14 @@
         <is>
           <t>NODE_S2014_15_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -14508,6 +14732,8 @@
           <t>NODE_S2015_16_0019</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14517,6 +14743,14 @@
         <is>
           <t>NODE_S2014_15_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -14550,6 +14784,8 @@
           <t>NODE_S2015_16_0019</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14559,6 +14795,14 @@
         <is>
           <t>NODE_S2014_15_0028</t>
         </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -15076,10 +15320,24 @@
           <t>NODE_S2015_16_0039</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0042</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -15113,10 +15371,28 @@
           <t>NODE_S2015_16_0039</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0049</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0047</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -15224,6 +15500,8 @@
           <t>NODE_S2015_16_0039</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15233,6 +15511,14 @@
         <is>
           <t>NODE_S2014_15_0152</t>
         </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -15303,10 +15589,20 @@
           <t>NODE_S2015_16_0039</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -15377,10 +15673,20 @@
           <t>NODE_S2015_16_0039</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -15525,10 +15831,24 @@
           <t>NODE_S2015_16_0051</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0054</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -15562,10 +15882,24 @@
           <t>NODE_S2015_16_0051</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0059</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -15747,10 +16081,24 @@
           <t>NODE_S2015_16_0051</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0062</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -15858,10 +16206,20 @@
           <t>NODE_S2015_16_0051</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -16043,10 +16401,24 @@
           <t>NODE_S2015_16_0065</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0068</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -16080,10 +16452,24 @@
           <t>NODE_S2015_16_0065</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0073</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -16265,10 +16651,24 @@
           <t>NODE_S2015_16_0065</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0076</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -16376,10 +16776,20 @@
           <t>NODE_S2015_16_0065</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="78">
@@ -16524,10 +16934,24 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0099</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -16561,10 +16985,24 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0084</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -16672,10 +17110,20 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="86">
@@ -16783,10 +17231,24 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0099</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -16820,10 +17282,24 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0081</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -17005,10 +17481,24 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0084</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="95">
@@ -17116,10 +17606,20 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="98">
@@ -17190,10 +17690,24 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0099</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -17227,10 +17741,24 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0088</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -17338,10 +17866,24 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0084</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="104">
@@ -17449,10 +17991,20 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="107">
@@ -17523,10 +18075,24 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0099</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -17560,10 +18126,20 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="110">
@@ -17597,10 +18173,20 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="111">
@@ -17634,10 +18220,24 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0099</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -17671,10 +18271,20 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="113">
@@ -17708,10 +18318,20 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="114">
@@ -17893,10 +18513,24 @@
           <t>NODE_S2015_16_0114</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0118</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>5 týmů</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -17930,10 +18564,28 @@
           <t>NODE_S2015_16_0114</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0123</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0121</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="120">
@@ -18041,10 +18693,20 @@
           <t>NODE_S2015_16_0114</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="123">
@@ -18115,10 +18777,20 @@
           <t>NODE_S2015_16_0114</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="125">
@@ -18295,10 +18967,24 @@
           <t>NODE_S2015_16_0126</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0129</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>4 týmů</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -18332,10 +19018,24 @@
           <t>NODE_S2015_16_0126</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0132</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="131">
@@ -18443,10 +19143,20 @@
           <t>NODE_S2015_16_0126</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="134">
@@ -18665,10 +19375,24 @@
           <t>NODE_S2015_16_0136</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0139</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -18702,10 +19426,28 @@
           <t>NODE_S2015_16_0136</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0146</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0144</t>
+        </is>
+      </c>
       <c r="J140" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="141">
@@ -18813,6 +19555,8 @@
           <t>NODE_S2015_16_0136</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18822,6 +19566,14 @@
         <is>
           <t>NODE_S2014_15_0152</t>
         </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="144">
@@ -18892,10 +19644,20 @@
           <t>NODE_S2015_16_0136</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="146">
@@ -18966,10 +19728,20 @@
           <t>NODE_S2015_16_0136</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="148">
@@ -19151,10 +19923,24 @@
           <t>NODE_S2015_16_0149</t>
         </is>
       </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0152</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -19188,10 +19974,24 @@
           <t>NODE_S2015_16_0149</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0155</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="154">
@@ -19299,10 +20099,28 @@
           <t>NODE_S2015_16_0149</t>
         </is>
       </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0160</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0158</t>
+        </is>
+      </c>
       <c r="J156" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="157">
@@ -19410,10 +20228,20 @@
           <t>NODE_S2015_16_0149</t>
         </is>
       </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="160">
@@ -19484,10 +20312,20 @@
           <t>NODE_S2015_16_0149</t>
         </is>
       </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="162">
@@ -19637,10 +20475,24 @@
           <t>NODE_S2015_16_0149</t>
         </is>
       </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0152</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -19790,10 +20642,24 @@
           <t>NODE_S2015_16_0166</t>
         </is>
       </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0171</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -19906,10 +20772,24 @@
           <t>NODE_S2015_16_0166</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0173</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -19980,10 +20860,24 @@
           <t>NODE_S2015_16_0166</t>
         </is>
       </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0176</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -20091,10 +20985,28 @@
           <t>NODE_S2015_16_0166</t>
         </is>
       </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0181</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0179</t>
+        </is>
+      </c>
       <c r="J177" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="178">
@@ -20202,10 +21114,20 @@
           <t>NODE_S2015_16_0166</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="181">
@@ -20276,10 +21198,20 @@
           <t>NODE_S2015_16_0166</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="183">
@@ -20392,10 +21324,24 @@
           <t>NODE_S2015_16_0166</t>
         </is>
       </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0176</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -20577,10 +21523,28 @@
           <t>NODE_S2015_16_0166</t>
         </is>
       </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0181</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0179</t>
+        </is>
+      </c>
       <c r="J190" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="191">
@@ -20688,10 +21652,20 @@
           <t>NODE_S2015_16_0166</t>
         </is>
       </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N193" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="194">
@@ -20762,10 +21736,20 @@
           <t>NODE_S2015_16_0166</t>
         </is>
       </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="196">
@@ -20947,10 +21931,24 @@
           <t>NODE_S2015_16_0196</t>
         </is>
       </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0200</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -20984,10 +21982,28 @@
           <t>NODE_S2015_16_0196</t>
         </is>
       </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0205</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0203</t>
+        </is>
+      </c>
       <c r="J201" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="202">
@@ -21095,10 +22111,20 @@
           <t>NODE_S2015_16_0196</t>
         </is>
       </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N204" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="205">
@@ -21169,10 +22195,20 @@
           <t>NODE_S2015_16_0196</t>
         </is>
       </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="207">
@@ -21317,10 +22353,24 @@
           <t>NODE_S2015_16_0207</t>
         </is>
       </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0210</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N210" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -21354,10 +22404,24 @@
           <t>NODE_S2015_16_0207</t>
         </is>
       </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0215</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="212">
@@ -21539,10 +22603,24 @@
           <t>NODE_S2015_16_0207</t>
         </is>
       </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0218</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N216" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="217">
@@ -21650,10 +22728,20 @@
           <t>NODE_S2015_16_0207</t>
         </is>
       </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="220">

--- a/data/S2015_16_FINAL.xlsx
+++ b/data/S2015_16_FINAL.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -13625,7 +13625,6 @@
           <t>NODE_S2015_16_0006</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13736,8 +13735,6 @@
           <t>NODE_S2015_16_0003</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13788,8 +13785,6 @@
           <t>NODE_S2015_16_0003</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13840,8 +13835,6 @@
           <t>NODE_S2015_16_0001</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14101,7 +14094,6 @@
           <t>NODE_S2015_16_0015</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14157,7 +14149,6 @@
           <t>NODE_S2015_16_0016</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14208,8 +14199,6 @@
           <t>NODE_S2015_16_0011</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14260,8 +14249,6 @@
           <t>NODE_S2015_16_0011</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14569,7 +14556,6 @@
           <t>NODE_S2015_16_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14625,7 +14611,6 @@
           <t>NODE_S2015_16_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14681,7 +14666,6 @@
           <t>NODE_S2015_16_0027</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14732,8 +14716,6 @@
           <t>NODE_S2015_16_0019</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14784,8 +14766,6 @@
           <t>NODE_S2015_16_0019</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15325,7 +15305,6 @@
           <t>NODE_S2015_16_0042</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15500,8 +15479,6 @@
           <t>NODE_S2015_16_0039</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15589,8 +15566,6 @@
           <t>NODE_S2015_16_0039</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15673,8 +15648,6 @@
           <t>NODE_S2015_16_0039</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15836,7 +15809,6 @@
           <t>NODE_S2015_16_0054</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15887,7 +15859,6 @@
           <t>NODE_S2015_16_0059</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16086,7 +16057,6 @@
           <t>NODE_S2015_16_0062</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16206,8 +16176,6 @@
           <t>NODE_S2015_16_0051</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16406,7 +16374,6 @@
           <t>NODE_S2015_16_0068</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16457,7 +16424,6 @@
           <t>NODE_S2015_16_0073</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16656,7 +16622,6 @@
           <t>NODE_S2015_16_0076</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16776,8 +16741,6 @@
           <t>NODE_S2015_16_0065</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16939,7 +16902,6 @@
           <t>NODE_S2015_16_0099</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16990,7 +16952,6 @@
           <t>NODE_S2015_16_0084</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17110,8 +17071,6 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17236,7 +17195,6 @@
           <t>NODE_S2015_16_0099</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17287,7 +17245,6 @@
           <t>NODE_S2015_16_0081</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17486,7 +17443,6 @@
           <t>NODE_S2015_16_0084</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17606,8 +17562,6 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17695,7 +17649,6 @@
           <t>NODE_S2015_16_0099</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17746,7 +17699,6 @@
           <t>NODE_S2015_16_0088</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17871,7 +17823,6 @@
           <t>NODE_S2015_16_0084</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17991,8 +17942,6 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18080,7 +18029,6 @@
           <t>NODE_S2015_16_0099</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18126,8 +18074,6 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18173,8 +18119,6 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18225,7 +18169,6 @@
           <t>NODE_S2015_16_0099</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18271,8 +18214,6 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18318,8 +18259,6 @@
           <t>NODE_S2015_16_0078</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18518,7 +18457,6 @@
           <t>NODE_S2015_16_0118</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18693,8 +18631,6 @@
           <t>NODE_S2015_16_0114</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18777,8 +18713,6 @@
           <t>NODE_S2015_16_0114</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18972,7 +18906,6 @@
           <t>NODE_S2015_16_0129</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19023,7 +18956,6 @@
           <t>NODE_S2015_16_0132</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19143,8 +19075,6 @@
           <t>NODE_S2015_16_0126</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19380,7 +19310,6 @@
           <t>NODE_S2015_16_0139</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19555,8 +19484,6 @@
           <t>NODE_S2015_16_0136</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19644,8 +19571,6 @@
           <t>NODE_S2015_16_0136</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19728,8 +19653,6 @@
           <t>NODE_S2015_16_0136</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19928,7 +19851,6 @@
           <t>NODE_S2015_16_0152</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19979,7 +19901,6 @@
           <t>NODE_S2015_16_0155</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20228,8 +20149,6 @@
           <t>NODE_S2015_16_0149</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20312,8 +20231,6 @@
           <t>NODE_S2015_16_0149</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20480,7 +20397,6 @@
           <t>NODE_S2015_16_0152</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20647,7 +20563,6 @@
           <t>NODE_S2015_16_0171</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20777,7 +20692,6 @@
           <t>NODE_S2015_16_0173</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20865,7 +20779,6 @@
           <t>NODE_S2015_16_0176</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21114,8 +21027,6 @@
           <t>NODE_S2015_16_0166</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21198,8 +21109,6 @@
           <t>NODE_S2015_16_0166</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21329,7 +21238,6 @@
           <t>NODE_S2015_16_0176</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21652,8 +21560,6 @@
           <t>NODE_S2015_16_0166</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21736,8 +21642,6 @@
           <t>NODE_S2015_16_0166</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21936,7 +21840,6 @@
           <t>NODE_S2015_16_0200</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22111,8 +22014,6 @@
           <t>NODE_S2015_16_0196</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22195,8 +22096,6 @@
           <t>NODE_S2015_16_0196</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22358,7 +22257,6 @@
           <t>NODE_S2015_16_0210</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22409,7 +22307,6 @@
           <t>NODE_S2015_16_0215</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22608,7 +22505,6 @@
           <t>NODE_S2015_16_0218</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22728,8 +22624,6 @@
           <t>NODE_S2015_16_0207</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
           <t>complete</t>
@@ -40913,7 +40807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40985,6 +40879,18 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>3 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bílí Tygři Liberec</t>
         </is>
       </c>
     </row>

--- a/data/S2015_16_FINAL.xlsx
+++ b/data/S2015_16_FINAL.xlsx
@@ -3693,7 +3693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4749,6 +4749,73 @@
       <c r="V19" s="2" t="n"/>
       <c r="W19" s="2" t="n"/>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0223</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HC TS Varnsdorf</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0223</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0277</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00277</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4760,7 +4827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W41"/>
+  <dimension ref="A1:W44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7295,6 +7362,118 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0224</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TJ Orli Lanškroun</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0224</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0278</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00278</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>HC Skuteč</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0224</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0279</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00279</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7306,7 +7485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W50"/>
+  <dimension ref="A1:W62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10028,6 +10207,500 @@
       <c r="V50" s="2" t="n"/>
       <c r="W50" s="2" t="n"/>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0225</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0225</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0280</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00280</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>6</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0225</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0281</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00281</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>10</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>HC Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0225</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0282</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00282</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0226</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>HC Litomyšl B</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0226</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0283</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00283</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0226</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0284</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00284</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0226</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0285</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00285</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Slovan Moravská Třebová B</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0226</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0286</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00286</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>5</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0226</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0287</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00287</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>6</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>IHC Česká Třebová</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0226</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0288</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00288</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>7</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0226</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0289</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00289</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10039,7 +10712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11093,6 +11766,857 @@
       <c r="U18" s="2" t="n"/>
       <c r="V18" s="2" t="n"/>
       <c r="W18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0227</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>soutěž nehrána</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0227</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0290</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00290</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HC Veverská Bítýška</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0227</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0291</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00291</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0227</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0292</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00292</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0228</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0228</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0293</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00293</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HAS Jihlava</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0228</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0294</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00294</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0228</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0295</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00295</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0228</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0296</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00296</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0228</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0297</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00297</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0228</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0298</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00298</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>7</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>HC Fan Club Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0228</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0299</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00299</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Hellfis Třebíč</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0228</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0300</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00300</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Horní Heřmanice</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0228</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0301</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00301</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>HPH Pokojovice</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0228</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0302</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00302</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0228</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0303</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00303</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0228</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0304</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00304</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Veselý TEAM</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0228</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0305</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00305</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>7</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Krhov</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0228</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0306</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00306</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>HC Drakstav</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0228</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0307</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00307</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13310,7 +14834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N222"/>
+  <dimension ref="A1:N229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22746,6 +24270,265 @@
       <c r="J222" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0222</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Praha – Pražský přebor</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>REG_PHA</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0039</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Liberecký – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>REG_LBK</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0136</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0224</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Hradecký – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>REG_HKK</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0149</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Pardubický – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>REG_PAK</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0166</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0226</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Pardubický – Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>REG_PAK</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0166</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0227</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Vysočina – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0196</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0228</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Vysočina – Jihlava</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0196</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -27768,7 +29551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J276"/>
+  <dimension ref="A1:J308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="8" max="8"/>
@@ -40793,6 +42576,870 @@
       <c r="J276" t="inlineStr">
         <is>
           <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0276</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Slovan Louny</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Slovan Louny</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>30PRAH</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0277</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>HC TS Varnsdorf</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>HC TS Varnsdorf</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>30LIBE</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0278</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>TJ Orli Lanškroun</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>TJ Orli Lanškroun</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>30HRAD</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0279</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>HC Skuteč</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>HC Skuteč</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>30HRAD</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0280</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0281</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0282</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>HC Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>HC Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0283</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>HC Litomyšl B</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>HC Litomyšl B</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0284</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0285</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0286</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Slovan Moravská Třebová B</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Slovan Moravská Třebová B</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0287</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0288</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>IHC Česká Třebová</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>IHC Česká Třebová</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0289</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0290</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>soutěž nehrána</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>soutěž nehrána</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0291</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>HC Veverská Bítýška</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>HC Veverská Bítýška</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0292</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0293</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0294</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>HAS Jihlava</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>HAS Jihlava</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0295</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0296</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0297</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0298</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0299</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>HC Fan Club Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>HC Fan Club Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0300</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Hellfis Třebíč</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Hellfis Třebíč</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0301</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Horní Heřmanice</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Horní Heřmanice</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0302</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>HPH Pokojovice</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>HPH Pokojovice</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0303</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0304</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0305</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Veselý TEAM</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Veselý TEAM</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0306</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Krhov</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Krhov</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0307</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>HC Drakstav</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>HC Drakstav</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>L40</t>
         </is>
       </c>
     </row>
@@ -45092,7 +47739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -46304,6 +48951,73 @@
       <c r="U21" s="2" t="n"/>
       <c r="V21" s="2" t="n"/>
       <c r="W21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pražský přebor</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0222</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Slovan Louny</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Pražský přebor</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0222</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>CLUB_S2015_16_0276</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>TR_S2015_16_00276</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/S2015_16_FINAL.xlsx
+++ b/data/S2015_16_FINAL.xlsx
@@ -40,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +59,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +86,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -95,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,6 +115,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -43552,7 +43563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -43609,11 +43620,89 @@
           <t>NODE_S2015_16_0031</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Praha – Pražský přebor (Praha) · NODE_S2015_16_0222</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (Slovan Louny), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Liberecký – Krajská liga (Liberecký kraj) · NODE_S2015_16_0223</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (HC TS Varnsdorf), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Hradecký – Krajská liga (Královéhradecký kraj) · NODE_S2015_16_0224</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (TJ Orli Lanškroun, HC Skuteč), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F2"/>

--- a/data/S2015_16_FINAL.xlsx
+++ b/data/S2015_16_FINAL.xlsx
@@ -104,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -117,6 +117,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -14770,7 +14773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14829,6 +14832,57 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0222</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (Slovan Louny), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0223</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (HC TS Varnsdorf), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0224</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (TJ Orli Lanškroun, HC Skuteč), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -43640,7 +43694,7 @@
           <t>Praha – Pražský přebor (Praha) · NODE_S2015_16_0222</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>máme jen 1 tým (Slovan Louny), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -43666,7 +43720,7 @@
           <t>Liberecký – Krajská liga (Liberecký kraj) · NODE_S2015_16_0223</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>máme jen 1 tým (HC TS Varnsdorf), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -43692,7 +43746,7 @@
           <t>Hradecký – Krajská liga (Královéhradecký kraj) · NODE_S2015_16_0224</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (TJ Orli Lanškroun, HC Skuteč), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>

--- a/data/S2015_16_FINAL.xlsx
+++ b/data/S2015_16_FINAL.xlsx
@@ -16787,7 +16787,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -16971,7 +16971,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HC Letci Letňany – SK Žižkov Praha  9:3,6:3</t>
+          <t>HC Letci Letňany – SK Žižkov Praha 9:3,6:3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -17008,7 +17008,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Hvězda Praha  - Bohemians Praha  9:1,7:1</t>
+          <t>Hvězda Praha - Bohemians Praha 9:1,7:1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -17095,7 +17095,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kobra Praha "B" – HC Olympik Mělník  8:9 SN,12:4,6:3</t>
+          <t>Kobra Praha "B" – HC Olympik Mělník 8:9 SN,12:4,6:3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bohemians Praha  - SK Žižkov Praha  8:5,2:4,3:7</t>
+          <t>Bohemians Praha - SK Žižkov Praha 8:5,2:4,3:7</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -17787,7 +17787,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HC Junior Mělník – SK Černošice  2:1,3:1</t>
+          <t>HC Junior Mělník – SK Černošice 2:1,3:1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -17861,7 +17861,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -18035,7 +18035,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>David servis České Budějovice  - OLH Spartak Soběslav 9:3,9:3</t>
+          <t>David servis České Budějovice - OLH Spartak Soběslav 9:3,9:3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -18072,7 +18072,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lokomotiva Veselí nad Lužnicí – HC Tábor "B"  3:2 PP,1:2,5:3</t>
+          <t>Lokomotiva Veselí nad Lužnicí – HC Tábor "B" 3:2 PP,1:2,5:3</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -18109,7 +18109,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HC Milevsko 2010 – Sokol Radomyšl  6:4,7:3</t>
+          <t>HC Milevsko 2010 – Sokol Radomyšl 6:4,7:3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -18146,7 +18146,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Slavoj Český Krumlov – Jiskra Humpolec  6:0,3:1</t>
+          <t>Slavoj Český Krumlov – Jiskra Humpolec 6:0,3:1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -18233,7 +18233,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>David servis České Budějovice  - Slavoj Český Krumlov  12:2,3:4,12:3</t>
+          <t>David servis České Budějovice - Slavoj Český Krumlov 12:2,3:4,12:3</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -18270,7 +18270,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lokomotiva Veselí nad Lužnicí  - HC Milevsko 2010  6:2,4:5 PP,3:8</t>
+          <t>Lokomotiva Veselí nad Lužnicí - HC Milevsko 2010 6:2,4:5 PP,3:8</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -18352,7 +18352,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>David servis České Budějovice  - HC Milevsko 2010  6:0,7:4</t>
+          <t>David servis České Budějovice - HC Milevsko 2010 6:0,7:4</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -18389,7 +18389,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40</t>
+          <t>Plzeňský, 4. úroveň</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -19310,7 +19310,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>HC JAM Plzeň – HC Saxana Group  - TJ Baník Líně 3:5, 4:10</t>
+          <t>HC JAM Plzeň – HC Saxana Group - TJ Baník Líně 3:5, 4:10</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -19907,7 +19907,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>30_Karlovarský L40</t>
+          <t>Karlovarský, 4. úroveň</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -20398,7 +20398,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>30_Ústecký L40</t>
+          <t>Ústecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -20567,7 +20567,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HC Roudnice nad Labem – HC Lovosice  8:7 SN,6:2</t>
+          <t>HC Roudnice nad Labem – HC Lovosice 8:7 SN,6:2</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -20604,7 +20604,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SK Kadaň "B" – HC Slovan Louny  4:9,4:5 SN</t>
+          <t>SK Kadaň "B" – HC Slovan Louny 4:9,4:5 SN</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -20686,7 +20686,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>HC Roudnice nad Labem  - HC Slovan Louny 8:6,4:3 SN</t>
+          <t>HC Roudnice nad Labem - HC Slovan Louny 8:6,4:3 SN</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -20797,7 +20797,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>30_Liberecký L40</t>
+          <t>Liberecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -20976,7 +20976,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>HC Turnov 1931  - HC Lomnice nad Popelkou  4:3 PP,3:6,2:4</t>
+          <t>HC Turnov 1931 - HC Lomnice nad Popelkou 4:3 PP,3:6,2:4</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -21013,7 +21013,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>HC Česká Lípa - Slavoj Liberec   0:8,7:8</t>
+          <t>HC Česká Lípa - Slavoj Liberec 0:8,7:8</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -21100,7 +21100,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>HC TS Varnsdorf – HC Frýdlant  3:6,3:5</t>
+          <t>HC TS Varnsdorf – HC Frýdlant 3:6,3:5</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -21182,7 +21182,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>HC Turnov 1931 – HC Česká Lípa   3:8,3:4 SN</t>
+          <t>HC Turnov 1931 – HC Česká Lípa 3:8,3:4 SN</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -21264,7 +21264,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Slavoj Liberec – HC Lomnice nad Popelkou  3:6,3:5</t>
+          <t>Slavoj Liberec – HC Lomnice nad Popelkou 3:6,3:5</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -21338,7 +21338,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>30_Hradecký L40</t>
+          <t>Hradecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov – HC Jičín   8:1,7:3</t>
+          <t>Stadion Nový Bydžov – HC Jičín 8:1,7:3</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -21549,7 +21549,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>HC Jaroměř – TJ BK Nová Paka  3:2,3:4,1:7</t>
+          <t>HC Jaroměř – TJ BK Nová Paka 3:2,3:4,1:7</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -21641,7 +21641,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>HC Rodos Dvůr Králové nad Labem – TJ BK Nová Paka  5:4,6:4,6:1</t>
+          <t>HC Rodos Dvůr Králové nad Labem – TJ BK Nová Paka 5:4,6:4,6:1</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>HC Náchod – Stadion Nový Bydžov  2:3 PP,5:4 PP,8:2,3:2</t>
+          <t>HC Náchod – Stadion Nový Bydžov 2:3 PP,5:4 PP,8:2,3:2</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -21760,7 +21760,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov – TJ BK Nová Paka  7:6,4:7,7:3</t>
+          <t>Stadion Nový Bydžov – TJ BK Nová Paka 7:6,4:7,7:3</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -22050,7 +22050,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>30_Pardubický L40</t>
+          <t>Pardubický, 4. úroveň</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -22303,7 +22303,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>HC Ledeč nad Sázavou  - Spartak Polička 6:1 (po dohodě jedno utkání)</t>
+          <t>HC Ledeč nad Sázavou - Spartak Polička 6:1 (po dohodě jedno utkání)</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -22390,7 +22390,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Spartak Choceň – Spartak Polička  7:6,5:6,6:3</t>
+          <t>Spartak Choceň – Spartak Polička 7:6,5:6,6:3</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -22427,7 +22427,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>HC Chotěboř – HC Ledeč nad Sázavou  5:7,5:6</t>
+          <t>HC Chotěboř – HC Ledeč nad Sázavou 5:7,5:6</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -22556,7 +22556,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>HC Hlinsko – Spartak Choceň  6:4,4:2</t>
+          <t>HC Hlinsko – Spartak Choceň 6:4,4:2</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>HC Ledeč nad Sázavou  - Spartak Choceň 2:5, 4:11</t>
+          <t>HC Ledeč nad Sázavou - Spartak Choceň 2:5, 4:11</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -22720,7 +22720,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>HC Chrudim – HC Hlinsko  7:6 PP,1:3,5:2</t>
+          <t>HC Chrudim – HC Hlinsko 7:6 PP,1:3,5:2</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -22849,7 +22849,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>HC Světlá nad Sázavou – HC Chotěboř  10:0,6:5,2:1 PP</t>
+          <t>HC Světlá nad Sázavou – HC Chotěboř 10:0,6:5,2:1 PP</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -22886,7 +22886,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Slovan Moravská Třebová – Spartak Choceň  7:5,7:3,3:4 SN,4:5 PP,5:2</t>
+          <t>Slovan Moravská Třebová – Spartak Choceň 7:5,7:3,3:4 SN,4:5 PP,5:2</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -22923,7 +22923,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Kohouti Česká Třebová – HC Hlinsko  8:0,2:3,9:3,7:5</t>
+          <t>Kohouti Česká Třebová – HC Hlinsko 8:0,2:3,9:3,7:5</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -22960,7 +22960,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>HC Chrudim – HC Litomyšl  4:5,2:7,5:4,1:2</t>
+          <t>HC Chrudim – HC Litomyšl 4:5,2:7,5:4,1:2</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>HC Světlá nad Sázavou  - HC Litomyšl 6:5 SN,0:2,5:1,4:6,4:2</t>
+          <t>HC Světlá nad Sázavou - HC Litomyšl 6:5 SN,0:2,5:1,4:6,4:2</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -23089,7 +23089,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Slovan Moravská Třebová – Kohouti Česká Třebová  5:4,3:11,6:3,2:3,5:4 PP</t>
+          <t>Slovan Moravská Třebová – Kohouti Česká Třebová 5:4,3:11,6:3,2:3,5:4 PP</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -23253,7 +23253,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>HC Světlá nad Sázavou  - Slovan Moravská Třebová  3:4 PP,2:5,3:5</t>
+          <t>HC Světlá nad Sázavou - Slovan Moravská Třebová 3:4 PP,2:5,3:5</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -23290,7 +23290,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>30_Vysočina L40</t>
+          <t>Vysočina, 4. úroveň</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -23918,7 +23918,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>HC Spartak Velká Bíteš – HC Lvi Břeclav "B"  9:3,4:2</t>
+          <t>HC Spartak Velká Bíteš – HC Lvi Břeclav "B" 9:3,4:2</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -23955,7 +23955,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>SK Minerva Boskovice – Dynamiters Blansko HK  5:2,3:2</t>
+          <t>SK Minerva Boskovice – Dynamiters Blansko HK 5:2,3:2</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -23992,7 +23992,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí – HK Kroměříž  6:4,1:6,5:1</t>
+          <t>HHK Velké Meziříčí – HK Kroměříž 6:4,1:6,5:1</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -24029,7 +24029,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Hokej Uherský Ostroh – HC Spartak Uherský Brod  3:1,1:6,8:3</t>
+          <t>Hokej Uherský Ostroh – HC Spartak Uherský Brod 3:1,1:6,8:3</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>HC Spartak Velká Bíteš – Hokej Uherský Ostroh  3:6,2:3</t>
+          <t>HC Spartak Velká Bíteš – Hokej Uherský Ostroh 3:6,2:3</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -24153,7 +24153,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>SK Minerva Boskovice – HHK Velké Meziříčí  0:1,5:6</t>
+          <t>SK Minerva Boskovice – HHK Velké Meziříčí 0:1,5:6</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -24235,7 +24235,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí – Hokej Uherský Ostroh  4:3,5:2</t>
+          <t>HHK Velké Meziříčí – Hokej Uherský Ostroh 4:3,5:2</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -24272,7 +24272,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">

--- a/data/S2015_16_FINAL.xlsx
+++ b/data/S2015_16_FINAL.xlsx
@@ -818,7 +818,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -27681,7 +27681,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -27754,7 +27754,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -27827,7 +27827,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -27905,7 +27905,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -27978,7 +27978,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -28056,7 +28056,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -28129,7 +28129,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -28202,7 +28202,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -28275,7 +28275,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -28348,7 +28348,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -28421,7 +28421,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -28494,7 +28494,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -28567,7 +28567,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -28640,7 +28640,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -48169,7 +48169,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -48242,7 +48242,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -48388,7 +48388,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -48461,7 +48461,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -48534,7 +48534,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -48607,7 +48607,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -48680,7 +48680,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -48753,7 +48753,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -49464,7 +49464,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -49537,7 +49537,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -49610,7 +49610,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -49683,7 +49683,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -49756,7 +49756,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -49829,7 +49829,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -49902,7 +49902,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -49975,7 +49975,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -50053,7 +50053,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -50126,7 +50126,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -50199,7 +50199,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -50272,7 +50272,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -54028,7 +54028,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -54106,7 +54106,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -54179,7 +54179,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -54252,7 +54252,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -54325,7 +54325,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -54398,7 +54398,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -54469,6 +54469,11 @@
           <t>CLUB_S2015_16_0137</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>play off</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr">
         <is>
           <t>TR_S2015_16_00137</t>
@@ -54539,7 +54544,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -54612,7 +54617,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -54685,7 +54690,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -54758,7 +54763,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
